--- a/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023</t>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,45</t>
+          <t>1,95; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,36</t>
+          <t>2,7; 9,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,22</t>
+          <t>2,82; 7,12</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,55</t>
+          <t>2,97; 8,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,18</t>
+          <t>3,08; 7,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,03</t>
+          <t>3,58; 7,21</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,68</t>
+          <t>2,25; 7,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 11,83</t>
+          <t>3,57; 12,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,31</t>
+          <t>3,53; 8,74</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 9,21</t>
+          <t>3,05; 8,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,44</t>
+          <t>4,33; 11,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,77</t>
+          <t>4,37; 8,85</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,59</t>
+          <t>3,5; 6,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,95</t>
+          <t>4,43; 7,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,68</t>
+          <t>4,47; 6,67</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2288; 8474</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3791; 13346</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7266; 18345</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9833</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22942</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5658; 16298</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7858; 20041</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15954; 32106</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11998</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20568</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4259; 14150</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6614; 22832</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13223; 32763</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9590</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13050</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22640</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5125; 14603</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7853; 20062</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15253; 30894</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>23273; 42140</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33747; 58792</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>63860; 95162</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,23</t>
+          <t>1,95; 7,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,5</t>
+          <t>2,61; 9,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,12</t>
+          <t>2,94; 7,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,55</t>
+          <t>3,0; 8,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,86</t>
+          <t>3,15; 7,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,21</t>
+          <t>3,73; 7,17</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,46</t>
+          <t>2,35; 7,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,32</t>
+          <t>3,32; 11,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,74</t>
+          <t>3,55; 8,45</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,69</t>
+          <t>3,25; 9,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,07</t>
+          <t>4,4; 11,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,85</t>
+          <t>4,58; 9,06</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,33</t>
+          <t>3,68; 6,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,72</t>
+          <t>4,54; 7,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,67</t>
+          <t>4,57; 6,68</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2288; 8474</t>
+          <t>2283; 8747</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3791; 13346</t>
+          <t>3659; 13637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7266; 18345</t>
+          <t>7573; 19074</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5658; 16298</t>
+          <t>5716; 15794</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7858; 20041</t>
+          <t>8042; 19507</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15954; 32106</t>
+          <t>16631; 31960</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4259; 14150</t>
+          <t>4447; 14912</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6614; 22832</t>
+          <t>6156; 21709</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13223; 32763</t>
+          <t>13318; 31676</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5125; 14603</t>
+          <t>5466; 15273</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7853; 20062</t>
+          <t>7967; 20713</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15253; 30894</t>
+          <t>16001; 31627</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23273; 42140</t>
+          <t>24459; 42378</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33747; 58792</t>
+          <t>34598; 59646</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63860; 95162</t>
+          <t>65252; 95291</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,46</t>
+          <t>2,49; 9,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 9,71</t>
+          <t>1,77; 7,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,4</t>
+          <t>2,8; 7,34</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,29</t>
+          <t>3,19; 8,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,65</t>
+          <t>2,87; 8,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,17</t>
+          <t>3,57; 6,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,87</t>
+          <t>3,5; 13,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,72</t>
+          <t>3,07; 9,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 8,45</t>
+          <t>3,91; 9,07</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,09</t>
+          <t>4,34; 10,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,43</t>
+          <t>3,31; 9,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,06</t>
+          <t>4,39; 8,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,37</t>
+          <t>4,51; 8,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,83</t>
+          <t>3,82; 6,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,68</t>
+          <t>4,6; 6,89</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11637</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2283; 8747</t>
+          <t>3140; 12437</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3659; 13637</t>
+          <t>2141; 8813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7573; 19074</t>
+          <t>6904; 18127</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>21460</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5716; 15794</t>
+          <t>7572; 19812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8042; 19507</t>
+          <t>5296; 15049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16631; 31960</t>
+          <t>15054; 29391</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>20234</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4447; 14912</t>
+          <t>5884; 22332</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6156; 21709</t>
+          <t>4800; 15018</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13318; 31676</t>
+          <t>12676; 29449</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>20937</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5466; 15273</t>
+          <t>7356; 18303</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7967; 20713</t>
+          <t>5529; 15346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16001; 31627</t>
+          <t>14770; 28195</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24459; 42378</t>
+          <t>31638; 56786</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34598; 59646</t>
+          <t>24045; 41922</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65252; 95291</t>
+          <t>61127; 91555</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,49; 9,88</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 7,28</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,8; 7,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,19; 8,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 8,16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,57; 6,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,5; 13,27</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,07; 9,61</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,91; 9,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,34; 10,81</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3,31; 9,18</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4,39; 8,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4,51; 8,1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3,82; 6,67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4,6; 6,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.05494852589523021</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.03897606008845</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.0471186234306806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6918</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11637</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.02493930353582912</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01768223762454606</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.02795273364500222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3140; 12437</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2141; 8813</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6904; 18127</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.09878026599971483</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.07278859599221828</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.07339533125139654</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.05207446590985196</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.04938732425422867</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05089913217206932</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12352</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9108</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21460</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.03192043401146064</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.02871590827113851</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03570484133333188</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7572; 19812</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5296; 15049</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15054; 29391</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.08352055306108758</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.08160538450416671</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.06971040863894037</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.06862485189349377</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.05557756847170126</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.06234517091323358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11552</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8681</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20234</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.03495232427679201</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.03073132328032461</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.03905871427287153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5884; 22332</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4800; 15018</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12676; 29449</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.132658705540794</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.09614279548218164</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.09073832110162526</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.06762715771254667</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05672969568597691</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.0622145601804073</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11454</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9482</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20937</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.04342877801083909</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.03308008076493846</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.04388880206507333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>7356; 18303</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5529; 15346</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>14770; 28195</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1080640541022896</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.09181503716952671</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.08378507407514732</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.06032501417363244</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05087209601216972</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.05585447652676521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>42278</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>31990</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>74268</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.04514342148206218</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.03823816378263876</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.045971918566699</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>31638; 56786</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>24045; 41922</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>61127; 91555</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.08102688993581103</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.06666710117630305</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.06885552562505644</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6918</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4719</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>11637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3140</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2141</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6904</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>12437</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>8813</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>18127</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>12352</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9108</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>21460</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>7572</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5296</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>15054</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>19812</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>15049</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>29391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>11552</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>20234</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>5884</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12676</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>22332</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>15018</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>29449</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11454</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9482</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>20937</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>7356</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5529</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>14770</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>18303</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>15346</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>28195</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>42278</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>74268</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>31638</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>24045</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>61127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>56786</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>41922</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>91555</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>